--- a/BOM_Board1_PCB1_2026-05-09.xlsx
+++ b/BOM_Board1_PCB1_2026-05-09.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE32746-3125-4C4A-BD5C-32E87D5EC588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8A18C1-81D3-4989-8603-F10808566230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_Board1_PCB1_2026-05-09" sheetId="1" r:id="rId1"/>
@@ -530,7 +530,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -570,7 +570,7 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -590,7 +590,7 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -610,7 +610,7 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -630,7 +630,7 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>29</v>
